--- a/storage/app/plantillas/plantilla_preconvalidacion_oficial.xlsx
+++ b/storage/app/plantillas/plantilla_preconvalidacion_oficial.xlsx
@@ -1,40 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LEGION\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3E93F6-73CE-44BF-B44C-12F45994B41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="1" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Preconvalidación" sheetId="1" r:id="rId1"/>
-    <sheet name="Cursos no convalidados" sheetId="2" r:id="rId2"/>
+    <sheet name="Preconvalidación" sheetId="1" r:id="rId4"/>
+    <sheet name="Cursos no convalidados" sheetId="2" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029" forceFullCalc="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="23">
   <si>
     <t>Facultad de Ingeniería e Inteligencia Artificial</t>
   </si>
@@ -103,44 +85,52 @@
   </si>
   <si>
     <t>Nota</t>
-  </si>
-  <si>
-    <t>Motivo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -158,6 +148,9 @@
         <fgColor rgb="FFF2F2F2"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">
@@ -224,48 +217,41 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+  <cellXfs count="14">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -555,17 +541,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:D29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.7265625" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="37.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="56.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8" customWidth="true" style="0"/>
+    <col min="2" max="2" width="37.08984375" customWidth="true" style="0"/>
+    <col min="3" max="3" width="56.6328125" customWidth="true" style="0"/>
+    <col min="4" max="4" width="7.81640625" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" customHeight="1" ht="15.5">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -573,7 +562,7 @@
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
     </row>
-    <row r="2" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" customHeight="1" ht="15.5">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
@@ -581,7 +570,7 @@
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
     </row>
-    <row r="3" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" customHeight="1" ht="15.5">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
@@ -589,7 +578,7 @@
       <c r="C3" s="9"/>
       <c r="D3" s="9"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4">
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
@@ -597,7 +586,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4">
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
@@ -605,7 +594,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4">
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
@@ -613,7 +602,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4">
       <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
@@ -621,7 +610,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
@@ -629,7 +618,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4">
       <c r="B9" s="1" t="s">
         <v>13</v>
       </c>
@@ -637,7 +626,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4">
       <c r="A10" s="4" t="s">
         <v>15</v>
       </c>
@@ -651,115 +640,115 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4">
       <c r="A11" s="5"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="5"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4">
       <c r="A12" s="5"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4">
       <c r="A13" s="5"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="5"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4">
       <c r="A14" s="5"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4">
       <c r="A15" s="5"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="5"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4">
       <c r="A16" s="5"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4">
       <c r="A17" s="5"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4">
       <c r="A18" s="5"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="5"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4">
       <c r="A19" s="5"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="5"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4">
       <c r="A20" s="5"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4">
       <c r="A21" s="5"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="5"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4">
       <c r="A22" s="5"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="5"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4">
       <c r="A23" s="5"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="5"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4">
       <c r="A24" s="5"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="5"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4">
       <c r="A25" s="5"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="5"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4">
       <c r="A26" s="5"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="5"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4">
       <c r="A27" s="5"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="5"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4">
       <c r="A28" s="5"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="5"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4">
       <c r="A29" s="10" t="s">
         <v>19</v>
       </c>
@@ -768,37 +757,50 @@
       <c r="D29" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A29:C29"/>
   </mergeCells>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="landscape" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" r:id="rId1ps"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:D60"/>
+  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.7265625" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="49.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="49.90625" customWidth="true" style="0"/>
+    <col min="2" max="2" width="4.90625" customWidth="true" style="0"/>
+    <col min="3" max="3" width="7.81640625" customWidth="true" style="0"/>
+    <col min="4" max="4" width="14.08984375" hidden="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" customHeight="1" ht="15.5">
       <c r="A1" s="7" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D1"/>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>21</v>
       </c>
@@ -808,333 +810,356 @@
       <c r="C2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D2" s="13"/>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="3"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D3"/>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="3"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D4"/>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="3"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D5"/>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="3"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D6"/>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="3"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D7"/>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="3"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D8"/>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="3"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D9"/>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="3"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D10"/>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="3"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D11"/>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="3"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D12"/>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="3"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
-      <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D13"/>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="3"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
-      <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D14"/>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" s="3"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D15"/>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="3"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D16"/>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" s="3"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D17"/>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" s="3"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D18"/>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" s="3"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D19"/>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" s="3"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D20"/>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" s="3"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D21"/>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" s="3"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D22"/>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" s="3"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="3"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D23"/>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" s="3"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="3"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D24"/>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" s="3"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
-      <c r="D25" s="3"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D25"/>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" s="3"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
-      <c r="D26" s="3"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D26"/>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" s="3"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="3"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D27"/>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" s="3"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="3"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D28"/>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29" s="3"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="3"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D29"/>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30" s="3"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="3"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D30"/>
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31" s="3"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="3"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D31"/>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32" s="3"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="3"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D32"/>
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33" s="3"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
-      <c r="D33" s="3"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D33"/>
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34" s="3"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
-      <c r="D34" s="3"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D34"/>
+    </row>
+    <row r="35" spans="1:4">
       <c r="A35" s="3"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
-      <c r="D35" s="3"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D35"/>
+    </row>
+    <row r="36" spans="1:4">
       <c r="A36" s="3"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
-      <c r="D36" s="3"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D36"/>
+    </row>
+    <row r="37" spans="1:4">
       <c r="A37" s="3"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
-      <c r="D37" s="3"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D37"/>
+    </row>
+    <row r="38" spans="1:4">
       <c r="A38" s="3"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
-      <c r="D38" s="3"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D38"/>
+    </row>
+    <row r="39" spans="1:4">
       <c r="A39" s="3"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
-      <c r="D39" s="3"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D39"/>
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40" s="3"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
-      <c r="D40" s="3"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D40"/>
+    </row>
+    <row r="41" spans="1:4">
       <c r="A41" s="3"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
-      <c r="D41" s="3"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D41"/>
+    </row>
+    <row r="42" spans="1:4">
       <c r="A42" s="3"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
-      <c r="D42" s="3"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D42"/>
+    </row>
+    <row r="43" spans="1:4">
       <c r="A43" s="3"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
-      <c r="D43" s="3"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D43"/>
+    </row>
+    <row r="44" spans="1:4">
       <c r="A44" s="3"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
-      <c r="D44" s="3"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D44"/>
+    </row>
+    <row r="45" spans="1:4">
       <c r="A45" s="3"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
-      <c r="D45" s="3"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D45"/>
+    </row>
+    <row r="46" spans="1:4">
       <c r="A46" s="3"/>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
-      <c r="D46" s="3"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D46"/>
+    </row>
+    <row r="47" spans="1:4">
       <c r="A47" s="3"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
-      <c r="D47" s="3"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D47"/>
+    </row>
+    <row r="48" spans="1:4">
       <c r="A48" s="3"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="3"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D48"/>
+    </row>
+    <row r="49" spans="1:4">
       <c r="A49" s="3"/>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="3"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D49"/>
+    </row>
+    <row r="50" spans="1:4">
       <c r="A50" s="3"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="3"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D50"/>
+    </row>
+    <row r="51" spans="1:4">
       <c r="A51" s="3"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
-      <c r="D51" s="3"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D51"/>
+    </row>
+    <row r="52" spans="1:4">
       <c r="A52" s="3"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
-      <c r="D52" s="3"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D52"/>
+    </row>
+    <row r="53" spans="1:4">
       <c r="A53" s="3"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
-      <c r="D53" s="3"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D53"/>
+    </row>
+    <row r="54" spans="1:4">
       <c r="A54" s="3"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="3"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D54"/>
+    </row>
+    <row r="55" spans="1:4">
       <c r="A55" s="3"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="3"/>
+      <c r="D55"/>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="D56"/>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="D57"/>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="D58"/>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="D59"/>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="D60"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells>
     <mergeCell ref="A1:D1"/>
   </mergeCells>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="landscape" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" r:id="rId1ps"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>